--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0148.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0148.xlsx
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Ta thách ngươi đấu tay đôi! Ta sẽ dạy cho ngươi biết thế nào là sự thanh nhã... TRÊN CHIẾN TRƯỜNG!</t>
+          <t>Ta thách ngươi đấu tay đôi! Ta sẽ dạy cho ngươi biết thế nào là sự thanh tao... TRÊN CHIẾN TRƯỜNG!</t>
         </is>
       </c>
     </row>
